--- a/artfynd/A 140-2024 artfynd.xlsx
+++ b/artfynd/A 140-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 140-2024 artfynd.xlsx
+++ b/artfynd/A 140-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101549795</v>
+        <v>101549723</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>103008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>645759.4818539645</v>
+        <v>645759</v>
       </c>
       <c r="R2" t="n">
-        <v>6710345.861552272</v>
+        <v>6710346</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -799,32 +794,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101549723</v>
+        <v>94551736</v>
       </c>
       <c r="B3" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -847,14 +837,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ledskärsområdet, Upl 2208 m NW, Ledskärsområdet, Upl</t>
+          <t>Ledskärsområdet, Upl 2351 m NW, Ledskärsområdet, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>645759.4818539645</v>
+        <v>645615</v>
       </c>
       <c r="R3" t="n">
-        <v>6710345.861552272</v>
+        <v>6710359</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,22 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>03:56</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>03:56</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,6 +910,244 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>101549726</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ledskärsområdet, Upl 2208 m NW, Ledskärsområdet, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>645759</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6710346</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>03:56</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>03:56</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>101549795</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ledskärsområdet, Upl 2208 m NW, Ledskärsområdet, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>645759</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6710346</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>03:56</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>03:56</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 140-2024 artfynd.xlsx
+++ b/artfynd/A 140-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101549723</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94551736</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101549726</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,8 +1168,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101549795</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>